--- a/human_resources_surveys/046_employee_incident_report_form--human_resources_surveys.xlsx
+++ b/human_resources_surveys/046_employee_incident_report_form--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -968,8 +968,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -997,12 +997,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'equipment_failure',_'label':_'equipment_failure'}</t>
+          <t>equipment_failure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Equipment Failure', 'label': 'Equipment Failure'}</t>
+          <t>Equipment Failure</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'human_error',_'label':_'human_error'}</t>
+          <t>human_error</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Human Error', 'label': 'Human Error'}</t>
+          <t>Human Error</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'hr',_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'HR', 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'immediate_supervisor',_'label':_'immediate_supervisor'}</t>
+          <t>immediate_supervisor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Immediate Supervisor', 'label': 'Immediate Supervisor'}</t>
+          <t>Immediate Supervisor</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'hr',_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'HR', 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
